--- a/public/formats/item_series.xlsx
+++ b/public/formats/item_series.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sdrimsac\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AED7B26-34F0-40D0-BACE-42A9893FF6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7650"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,16 +33,16 @@
     <t>Código Interno (Producto)</t>
   </si>
   <si>
-    <t>Desc Precio 1</t>
+    <t>Serie</t>
   </si>
   <si>
-    <t>Serie</t>
+    <t>codigo lote</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -352,8 +353,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -361,20 +362,26 @@
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
+      <c r="B2">
+        <v>46456757578</v>
+      </c>
+      <c r="C2">
+        <v>457567568</v>
       </c>
     </row>
   </sheetData>
